--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/05 Mayo/Dasboatdde abril/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="716" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09CCFEB-F04B-42F9-99CA-A38399CBEAA4}"/>
+  <xr:revisionPtr revIDLastSave="880" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{531E9210-7E34-472C-BFCF-1DA89CC37857}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="36">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -143,7 +143,10 @@
     <t>NUMERARIO</t>
   </si>
   <si>
-    <t>Marzo</t>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN CRISTOBAL </t>
   </si>
 </sst>
 </file>
@@ -530,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -601,7 +604,7 @@
         <v>28</v>
       </c>
       <c r="D4" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2">
         <v>2800</v>
@@ -635,7 +638,7 @@
         <v>30</v>
       </c>
       <c r="D6" s="2">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="E6" s="2">
         <v>2800</v>
@@ -669,7 +672,7 @@
         <v>27</v>
       </c>
       <c r="D8" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
         <v>2400</v>
@@ -686,7 +689,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2">
         <v>2400</v>
@@ -703,7 +706,7 @@
         <v>29</v>
       </c>
       <c r="D10" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2">
         <v>2400</v>
@@ -719,8 +722,8 @@
       <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D11">
-        <v>95</v>
+      <c r="D11" s="2">
+        <v>100</v>
       </c>
       <c r="E11" s="2">
         <v>2400</v>
@@ -754,7 +757,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2">
         <v>1350</v>
@@ -788,7 +791,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2">
         <v>1350</v>
@@ -804,8 +807,8 @@
       <c r="C16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D16">
-        <v>32</v>
+      <c r="D16" s="2">
+        <v>20</v>
       </c>
       <c r="E16" s="2">
         <v>1350</v>
@@ -825,7 +828,7 @@
         <v>800</v>
       </c>
       <c r="E17" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +842,10 @@
         <v>27</v>
       </c>
       <c r="D18" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -859,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +876,10 @@
         <v>29</v>
       </c>
       <c r="D20" s="2">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -889,11 +892,11 @@
       <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>135</v>
       </c>
       <c r="E21" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -974,8 +977,8 @@
       <c r="C26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D26">
-        <v>69</v>
+      <c r="D26" s="2">
+        <v>75</v>
       </c>
       <c r="E26" s="2">
         <v>1450</v>
@@ -1059,8 +1062,8 @@
       <c r="C31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D31">
-        <v>68</v>
+      <c r="D31" s="2">
+        <v>80</v>
       </c>
       <c r="E31" s="2">
         <v>1500</v>
@@ -1128,7 +1131,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="2">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="E35" s="2">
         <v>4000</v>
@@ -1144,8 +1147,8 @@
       <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D36">
-        <v>176</v>
+      <c r="D36" s="2">
+        <v>180</v>
       </c>
       <c r="E36" s="2">
         <v>4000</v>
@@ -1165,7 +1168,7 @@
         <v>1500</v>
       </c>
       <c r="E37" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1182,10 @@
         <v>27</v>
       </c>
       <c r="D38" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E38" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1199,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,10 +1216,10 @@
         <v>29</v>
       </c>
       <c r="D40" s="2">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1229,11 +1232,11 @@
       <c r="C41" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D41">
-        <v>98</v>
+      <c r="D41" s="2">
+        <v>90</v>
       </c>
       <c r="E41" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1298,7 +1301,7 @@
         <v>29</v>
       </c>
       <c r="D45" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2">
         <v>2000</v>
@@ -1314,8 +1317,8 @@
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D46">
-        <v>128</v>
+      <c r="D46" s="2">
+        <v>130</v>
       </c>
       <c r="E46" s="2">
         <v>2000</v>
@@ -1349,7 +1352,7 @@
         <v>27</v>
       </c>
       <c r="D48" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E48" s="2">
         <v>1500</v>
@@ -1399,8 +1402,8 @@
       <c r="C51" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D51">
-        <v>54</v>
+      <c r="D51" s="2">
+        <v>65</v>
       </c>
       <c r="E51" s="2">
         <v>1500</v>
@@ -1468,7 +1471,7 @@
         <v>29</v>
       </c>
       <c r="D55" s="2">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E55" s="2">
         <v>2000</v>
@@ -1484,8 +1487,8 @@
       <c r="C56" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D56">
-        <v>60</v>
+      <c r="D56" s="2">
+        <v>70</v>
       </c>
       <c r="E56" s="2">
         <v>2000</v>
@@ -1569,8 +1572,8 @@
       <c r="C61" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D61">
-        <v>74</v>
+      <c r="D61" s="2">
+        <v>70</v>
       </c>
       <c r="E61" s="2">
         <v>1100</v>
@@ -1654,8 +1657,8 @@
       <c r="C66" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D66">
-        <v>183</v>
+      <c r="D66" s="2">
+        <v>200</v>
       </c>
       <c r="E66" s="2">
         <v>2200</v>
@@ -1723,7 +1726,7 @@
         <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E70" s="2">
         <v>1600</v>
@@ -1739,8 +1742,8 @@
       <c r="C71" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D71">
-        <v>168</v>
+      <c r="D71" s="2">
+        <v>160</v>
       </c>
       <c r="E71" s="2">
         <v>1600</v>
@@ -1808,7 +1811,7 @@
         <v>29</v>
       </c>
       <c r="D75" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E75" s="2">
         <v>2200</v>
@@ -1824,8 +1827,8 @@
       <c r="C76" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D76">
-        <v>92</v>
+      <c r="D76" s="2">
+        <v>90</v>
       </c>
       <c r="E76" s="2">
         <v>2200</v>
@@ -1859,7 +1862,7 @@
         <v>27</v>
       </c>
       <c r="D78" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E78" s="2">
         <v>2850</v>
@@ -1876,7 +1879,7 @@
         <v>28</v>
       </c>
       <c r="D79" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E79" s="2">
         <v>2850</v>
@@ -1893,7 +1896,7 @@
         <v>29</v>
       </c>
       <c r="D80" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2">
         <v>2850</v>
@@ -1909,8 +1912,8 @@
       <c r="C81" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D81">
-        <v>129</v>
+      <c r="D81" s="2">
+        <v>150</v>
       </c>
       <c r="E81" s="2">
         <v>2850</v>
@@ -1960,7 +1963,7 @@
       <c r="C84" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="2">
         <v>10</v>
       </c>
       <c r="E84" s="2">
@@ -1978,7 +1981,7 @@
         <v>29</v>
       </c>
       <c r="D85" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E85" s="2">
         <v>3500</v>
@@ -1994,8 +1997,8 @@
       <c r="C86" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D86">
-        <v>183</v>
+      <c r="D86" s="2">
+        <v>210</v>
       </c>
       <c r="E86" s="2">
         <v>3500</v>
@@ -2046,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="D89" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E89" s="2">
         <v>3500</v>
@@ -2063,7 +2066,7 @@
         <v>29</v>
       </c>
       <c r="D90" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E90" s="2">
         <v>3500</v>
@@ -2079,8 +2082,8 @@
       <c r="C91" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D91">
-        <v>198</v>
+      <c r="D91" s="2">
+        <v>190</v>
       </c>
       <c r="E91" s="2">
         <v>3500</v>
@@ -2148,7 +2151,7 @@
         <v>29</v>
       </c>
       <c r="D95" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E95" s="2">
         <v>2300</v>
@@ -2164,8 +2167,8 @@
       <c r="C96" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D96">
-        <v>151</v>
+      <c r="D96" s="2">
+        <v>160</v>
       </c>
       <c r="E96" s="2">
         <v>2300</v>
@@ -2199,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="D98" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E98" s="2">
         <v>6000</v>
@@ -2233,7 +2236,7 @@
         <v>29</v>
       </c>
       <c r="D100" s="2">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E100" s="2">
         <v>6000</v>
@@ -2249,8 +2252,8 @@
       <c r="C101" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D101">
-        <v>192</v>
+      <c r="D101" s="2">
+        <v>400</v>
       </c>
       <c r="E101" s="2">
         <v>6000</v>
@@ -2301,7 +2304,7 @@
         <v>28</v>
       </c>
       <c r="D104" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E104" s="2">
         <v>2600</v>
@@ -2318,7 +2321,7 @@
         <v>29</v>
       </c>
       <c r="D105" s="2">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E105" s="2">
         <v>2600</v>
@@ -2334,8 +2337,8 @@
       <c r="C106" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D106">
-        <v>181</v>
+      <c r="D106" s="2">
+        <v>210</v>
       </c>
       <c r="E106" s="2">
         <v>2600</v>
@@ -2386,7 +2389,7 @@
         <v>28</v>
       </c>
       <c r="D109" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E109" s="2">
         <v>2650</v>
@@ -2403,7 +2406,7 @@
         <v>29</v>
       </c>
       <c r="D110" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E110" s="2">
         <v>2650</v>
@@ -2419,8 +2422,8 @@
       <c r="C111" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D111">
-        <v>126</v>
+      <c r="D111" s="2">
+        <v>120</v>
       </c>
       <c r="E111" s="2">
         <v>2650</v>
@@ -2431,16 +2434,16 @@
         <v>34</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D112">
-        <v>27700</v>
+      <c r="D112" s="2">
+        <v>0</v>
       </c>
       <c r="E112" s="2">
-        <v>53800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2448,16 +2451,16 @@
         <v>34</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D113">
-        <v>857</v>
+      <c r="D113" s="2">
+        <v>15</v>
       </c>
       <c r="E113" s="2">
-        <v>53800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2465,16 +2468,16 @@
         <v>34</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D114">
-        <v>131</v>
+      <c r="D114" s="2">
+        <v>4</v>
       </c>
       <c r="E114" s="2">
-        <v>53800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,16 +2485,16 @@
         <v>34</v>
       </c>
       <c r="B115" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D115" s="2">
-        <v>1858</v>
+        <v>30</v>
       </c>
       <c r="E115" s="2">
-        <v>53800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2499,16 +2502,16 @@
         <v>34</v>
       </c>
       <c r="B116" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D116">
-        <v>2738</v>
+      <c r="D116" s="2">
+        <v>70</v>
       </c>
       <c r="E116" s="2">
-        <v>53800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2516,16 +2519,16 @@
         <v>34</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D117" s="2">
-        <v>1500</v>
+      <c r="D117">
+        <v>27700</v>
       </c>
       <c r="E117" s="2">
-        <v>5700</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2533,16 +2536,16 @@
         <v>34</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D118">
-        <v>17</v>
+      <c r="D118" s="2">
+        <v>820</v>
       </c>
       <c r="E118" s="2">
-        <v>5700</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2550,16 +2553,16 @@
         <v>34</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D119" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="E119" s="2">
-        <v>5700</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2567,16 +2570,16 @@
         <v>34</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D120" s="2">
-        <v>1858</v>
+        <v>1637</v>
       </c>
       <c r="E120" s="2">
-        <v>5700</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2584,20 +2587,105 @@
         <v>34</v>
       </c>
       <c r="B121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" s="2">
+        <v>3085</v>
+      </c>
+      <c r="E121" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" t="s">
         <v>33</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D121">
-        <v>192</v>
-      </c>
-      <c r="E121" s="2">
-        <v>5700</v>
+      <c r="C122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1500</v>
+      </c>
+      <c r="E122" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" t="s">
+        <v>33</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" s="2">
+        <v>820</v>
+      </c>
+      <c r="E123" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
+        <v>33</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="2">
+        <v>136</v>
+      </c>
+      <c r="E124" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="2">
+        <v>1637</v>
+      </c>
+      <c r="E125" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>34</v>
+      </c>
+      <c r="B126" t="s">
+        <v>33</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="2">
+        <v>3085</v>
+      </c>
+      <c r="E126" s="2">
+        <v>53400</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/05 Mayo/Dasboatdde abril/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="880" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{531E9210-7E34-472C-BFCF-1DA89CC37857}"/>
+  <xr:revisionPtr revIDLastSave="952" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33AF4B0C-4B7D-42E9-A844-F40857C354B4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -143,10 +143,10 @@
     <t>NUMERARIO</t>
   </si>
   <si>
-    <t>Abril</t>
-  </si>
-  <si>
     <t xml:space="preserve">SAN CRISTOBAL </t>
+  </si>
+  <si>
+    <t>Mayo</t>
   </si>
 </sst>
 </file>
@@ -561,7 +561,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -573,12 +573,12 @@
         <v>1500</v>
       </c>
       <c r="E2" s="2">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -587,15 +587,15 @@
         <v>27</v>
       </c>
       <c r="D3" s="2">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E3" s="2">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -604,15 +604,15 @@
         <v>28</v>
       </c>
       <c r="D4" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -624,12 +624,12 @@
         <v>95</v>
       </c>
       <c r="E5" s="2">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
@@ -641,12 +641,12 @@
         <v>180</v>
       </c>
       <c r="E6" s="2">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>0</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>0</v>
@@ -680,7 +680,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2">
         <v>2400</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>0</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>0</v>
@@ -723,7 +723,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E11" s="2">
         <v>2400</v>
@@ -731,7 +731,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -743,12 +743,12 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -760,12 +760,12 @@
         <v>8</v>
       </c>
       <c r="E13" s="2">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -774,15 +774,15 @@
         <v>28</v>
       </c>
       <c r="D14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -794,12 +794,12 @@
         <v>40</v>
       </c>
       <c r="E15" s="2">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -808,15 +808,15 @@
         <v>30</v>
       </c>
       <c r="D16" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2">
-        <v>1350</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -842,7 +842,7 @@
         <v>27</v>
       </c>
       <c r="D18" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2">
         <v>1500</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -867,7 +867,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -918,7 +918,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -927,7 +927,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2">
         <v>1450</v>
@@ -935,7 +935,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
@@ -952,7 +952,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
@@ -978,7 +978,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2">
         <v>1450</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -1097,7 +1097,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2">
         <v>4000</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -1233,7 +1233,7 @@
         <v>30</v>
       </c>
       <c r="D41" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2">
         <v>2400</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -1258,7 +1258,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -1267,7 +1267,7 @@
         <v>27</v>
       </c>
       <c r="D43" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E43" s="2">
         <v>2000</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
@@ -1284,7 +1284,7 @@
         <v>28</v>
       </c>
       <c r="D44" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2">
         <v>2000</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -1369,7 +1369,7 @@
         <v>28</v>
       </c>
       <c r="D49" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2">
         <v>1500</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
@@ -1386,7 +1386,7 @@
         <v>29</v>
       </c>
       <c r="D50" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2">
         <v>1500</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
@@ -1403,7 +1403,7 @@
         <v>30</v>
       </c>
       <c r="D51" s="2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E51" s="2">
         <v>1500</v>
@@ -1411,7 +1411,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
@@ -1437,7 +1437,7 @@
         <v>27</v>
       </c>
       <c r="D53" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E53" s="2">
         <v>2000</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
@@ -1471,7 +1471,7 @@
         <v>29</v>
       </c>
       <c r="D55" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E55" s="2">
         <v>2000</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
         <v>18</v>
@@ -1522,7 +1522,7 @@
         <v>27</v>
       </c>
       <c r="D58" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E58" s="2">
         <v>1100</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B59" t="s">
         <v>18</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B60" t="s">
         <v>18</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B61" t="s">
         <v>18</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B62" t="s">
         <v>20</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
@@ -1607,7 +1607,7 @@
         <v>27</v>
       </c>
       <c r="D63" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E63" s="2">
         <v>2200</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
         <v>20</v>
@@ -1632,7 +1632,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
         <v>20</v>
@@ -1658,7 +1658,7 @@
         <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E66" s="2">
         <v>2200</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
@@ -1678,12 +1678,12 @@
         <v>1200</v>
       </c>
       <c r="E67" s="2">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
         <v>21</v>
@@ -1692,15 +1692,15 @@
         <v>27</v>
       </c>
       <c r="D68" s="2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E68" s="2">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B69" t="s">
         <v>21</v>
@@ -1709,15 +1709,15 @@
         <v>28</v>
       </c>
       <c r="D69" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E69" s="2">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
         <v>21</v>
@@ -1726,15 +1726,15 @@
         <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E70" s="2">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B71" t="s">
         <v>21</v>
@@ -1746,12 +1746,12 @@
         <v>160</v>
       </c>
       <c r="E71" s="2">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
@@ -1768,7 +1768,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
@@ -1777,7 +1777,7 @@
         <v>27</v>
       </c>
       <c r="D73" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73" s="2">
         <v>2200</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B75" t="s">
         <v>6</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B76" t="s">
         <v>6</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B77" t="s">
         <v>1</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
         <v>1</v>
@@ -1862,7 +1862,7 @@
         <v>27</v>
       </c>
       <c r="D78" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E78" s="2">
         <v>2850</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
         <v>1</v>
@@ -1879,7 +1879,7 @@
         <v>28</v>
       </c>
       <c r="D79" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E79" s="2">
         <v>2850</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
         <v>1</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
@@ -1929,16 +1929,16 @@
       <c r="C82" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="2">
         <v>1500</v>
       </c>
       <c r="E82" s="2">
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
@@ -1947,15 +1947,15 @@
         <v>27</v>
       </c>
       <c r="D83" s="2">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E83" s="2">
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
@@ -1967,12 +1967,12 @@
         <v>10</v>
       </c>
       <c r="E84" s="2">
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
@@ -1981,15 +1981,15 @@
         <v>29</v>
       </c>
       <c r="D85" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E85" s="2">
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
@@ -1998,15 +1998,15 @@
         <v>30</v>
       </c>
       <c r="D86" s="2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E86" s="2">
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
@@ -2032,7 +2032,7 @@
         <v>27</v>
       </c>
       <c r="D88" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E88" s="2">
         <v>3500</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
@@ -2049,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="D89" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E89" s="2">
         <v>3500</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
@@ -2066,7 +2066,7 @@
         <v>29</v>
       </c>
       <c r="D90" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E90" s="2">
         <v>3500</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
@@ -2091,7 +2091,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
@@ -2103,12 +2103,12 @@
         <v>1500</v>
       </c>
       <c r="E92" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
@@ -2117,15 +2117,15 @@
         <v>27</v>
       </c>
       <c r="D93" s="2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E93" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
@@ -2134,15 +2134,15 @@
         <v>28</v>
       </c>
       <c r="D94" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E94" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
@@ -2151,15 +2151,15 @@
         <v>29</v>
       </c>
       <c r="D95" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E95" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
@@ -2168,15 +2168,15 @@
         <v>30</v>
       </c>
       <c r="D96" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E96" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B97" t="s">
         <v>16</v>
@@ -2188,12 +2188,12 @@
         <v>1500</v>
       </c>
       <c r="E97" s="2">
-        <v>6000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
@@ -2202,15 +2202,15 @@
         <v>27</v>
       </c>
       <c r="D98" s="2">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="E98" s="2">
-        <v>6000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
@@ -2222,12 +2222,12 @@
         <v>14</v>
       </c>
       <c r="E99" s="2">
-        <v>6000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
@@ -2239,12 +2239,12 @@
         <v>220</v>
       </c>
       <c r="E100" s="2">
-        <v>6000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
@@ -2253,15 +2253,15 @@
         <v>30</v>
       </c>
       <c r="D101" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E101" s="2">
-        <v>6000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B102" t="s">
         <v>19</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
@@ -2304,7 +2304,7 @@
         <v>28</v>
       </c>
       <c r="D104" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E104" s="2">
         <v>2600</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
@@ -2321,7 +2321,7 @@
         <v>29</v>
       </c>
       <c r="D105" s="2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E105" s="2">
         <v>2600</v>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B106" t="s">
         <v>19</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
@@ -2372,7 +2372,7 @@
         <v>27</v>
       </c>
       <c r="D108" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E108" s="2">
         <v>2650</v>
@@ -2380,7 +2380,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B110" t="s">
         <v>15</v>
@@ -2406,7 +2406,7 @@
         <v>29</v>
       </c>
       <c r="D110" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E110" s="2">
         <v>2650</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
@@ -2423,7 +2423,7 @@
         <v>30</v>
       </c>
       <c r="D111" s="2">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E111" s="2">
         <v>2650</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>35</v>
+      </c>
+      <c r="B112" t="s">
         <v>34</v>
-      </c>
-      <c r="B112" t="s">
-        <v>35</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>22</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>35</v>
+      </c>
+      <c r="B113" t="s">
         <v>34</v>
-      </c>
-      <c r="B113" t="s">
-        <v>35</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>27</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>35</v>
+      </c>
+      <c r="B114" t="s">
         <v>34</v>
-      </c>
-      <c r="B114" t="s">
-        <v>35</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>28</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>35</v>
+      </c>
+      <c r="B115" t="s">
         <v>34</v>
-      </c>
-      <c r="B115" t="s">
-        <v>35</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>29</v>
@@ -2499,10 +2499,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>35</v>
+      </c>
+      <c r="B116" t="s">
         <v>34</v>
-      </c>
-      <c r="B116" t="s">
-        <v>35</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>30</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B117" t="s">
         <v>31</v>
@@ -2524,16 +2524,16 @@
       <c r="C117" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="2">
         <v>27700</v>
       </c>
       <c r="E117" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B118" t="s">
         <v>31</v>
@@ -2542,15 +2542,15 @@
         <v>27</v>
       </c>
       <c r="D118" s="2">
-        <v>820</v>
+        <v>930</v>
       </c>
       <c r="E118" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
         <v>31</v>
@@ -2559,15 +2559,15 @@
         <v>28</v>
       </c>
       <c r="D119" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="E119" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B120" t="s">
         <v>31</v>
@@ -2576,15 +2576,15 @@
         <v>29</v>
       </c>
       <c r="D120" s="2">
-        <v>1637</v>
+        <v>1712</v>
       </c>
       <c r="E120" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B121" t="s">
         <v>31</v>
@@ -2593,15 +2593,15 @@
         <v>30</v>
       </c>
       <c r="D121" s="2">
-        <v>3085</v>
+        <v>3255</v>
       </c>
       <c r="E121" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B122" t="s">
         <v>33</v>
@@ -2610,15 +2610,15 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>1500</v>
+        <v>27700</v>
       </c>
       <c r="E122" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B123" t="s">
         <v>33</v>
@@ -2627,15 +2627,15 @@
         <v>27</v>
       </c>
       <c r="D123" s="2">
-        <v>820</v>
+        <v>930</v>
       </c>
       <c r="E123" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B124" t="s">
         <v>33</v>
@@ -2644,15 +2644,15 @@
         <v>28</v>
       </c>
       <c r="D124" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="E124" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B125" t="s">
         <v>33</v>
@@ -2661,15 +2661,15 @@
         <v>29</v>
       </c>
       <c r="D125" s="2">
-        <v>1637</v>
+        <v>1712</v>
       </c>
       <c r="E125" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B126" t="s">
         <v>33</v>
@@ -2678,10 +2678,10 @@
         <v>30</v>
       </c>
       <c r="D126" s="2">
-        <v>3085</v>
+        <v>3255</v>
       </c>
       <c r="E126" s="2">
-        <v>53400</v>
+        <v>55650</v>
       </c>
     </row>
   </sheetData>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="952" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33AF4B0C-4B7D-42E9-A844-F40857C354B4}"/>
+  <xr:revisionPtr revIDLastSave="1001" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CD8210E-7EAE-46FE-9BCC-A78E6EBC242D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">SAN CRISTOBAL </t>
   </si>
   <si>
-    <t>Mayo</t>
+    <t>Junio</t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -570,7 +570,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="E2" s="2">
         <v>3000</v>
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="2">
         <v>1500</v>
@@ -910,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="2">
-        <v>1200</v>
+        <v>417</v>
       </c>
       <c r="E22" s="2">
         <v>1450</v>
@@ -1420,7 +1420,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="2">
         <v>2000</v>
@@ -1505,7 +1505,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="2">
-        <v>1200</v>
+        <v>835</v>
       </c>
       <c r="E57" s="2">
         <v>1100</v>
@@ -1675,7 +1675,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2">
-        <v>1200</v>
+        <v>1043</v>
       </c>
       <c r="E67" s="2">
         <v>1800</v>
@@ -1845,7 +1845,7 @@
         <v>22</v>
       </c>
       <c r="D77" s="2">
-        <v>1500</v>
+        <v>848</v>
       </c>
       <c r="E77" s="2">
         <v>2850</v>
@@ -2270,7 +2270,7 @@
         <v>22</v>
       </c>
       <c r="D102" s="2">
-        <v>1500</v>
+        <v>913</v>
       </c>
       <c r="E102" s="2">
         <v>2600</v>
@@ -2389,7 +2389,7 @@
         <v>28</v>
       </c>
       <c r="D109" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E109" s="2">
         <v>2650</v>
@@ -2525,7 +2525,7 @@
         <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>27700</v>
+        <v>25304</v>
       </c>
       <c r="E117" s="2">
         <v>55650</v>
@@ -2559,7 +2559,7 @@
         <v>28</v>
       </c>
       <c r="D119" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E119" s="2">
         <v>55650</v>
@@ -2610,7 +2610,7 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>27700</v>
+        <v>25304</v>
       </c>
       <c r="E122" s="2">
         <v>55650</v>
@@ -2644,7 +2644,7 @@
         <v>28</v>
       </c>
       <c r="D124" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E124" s="2">
         <v>55650</v>
@@ -2684,8 +2684,135 @@
         <v>55650</v>
       </c>
     </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+    </row>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+    </row>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+    </row>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+    </row>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E151" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/07 Julio/Dasboatdde julio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1001" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CD8210E-7EAE-46FE-9BCC-A78E6EBC242D}"/>
+  <xr:revisionPtr revIDLastSave="1004" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20B43C96-3321-4D1C-82A1-33A922D9EB26}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/07 Julio/Dasboatdde julio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/08 Agosto/Dasboatdde julio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1004" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20B43C96-3321-4D1C-82A1-33A922D9EB26}"/>
+  <xr:revisionPtr revIDLastSave="1006" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A94663-2454-4210-87D4-7DAD6321C297}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">SAN CRISTOBAL </t>
   </si>
   <si>
-    <t>Junio</t>
+    <t>Julio</t>
   </si>
 </sst>
 </file>
@@ -533,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -570,7 +570,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>848</v>
+        <v>1500</v>
       </c>
       <c r="E2" s="2">
         <v>3000</v>
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="2">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E17" s="2">
         <v>1500</v>
@@ -910,7 +910,7 @@
         <v>22</v>
       </c>
       <c r="D22" s="2">
-        <v>417</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="2">
         <v>1450</v>
@@ -1338,7 +1338,7 @@
         <v>1200</v>
       </c>
       <c r="E47" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1355,7 +1355,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1389,7 +1389,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1406,7 +1406,7 @@
         <v>70</v>
       </c>
       <c r="E51" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
         <v>22</v>
       </c>
       <c r="D52" s="2">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E52" s="2">
         <v>2000</v>
@@ -1505,7 +1505,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="2">
-        <v>835</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="2">
         <v>1100</v>
@@ -1675,7 +1675,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2">
-        <v>1043</v>
+        <v>1200</v>
       </c>
       <c r="E67" s="2">
         <v>1800</v>
@@ -1845,7 +1845,7 @@
         <v>22</v>
       </c>
       <c r="D77" s="2">
-        <v>848</v>
+        <v>1500</v>
       </c>
       <c r="E77" s="2">
         <v>2850</v>
@@ -2270,7 +2270,7 @@
         <v>22</v>
       </c>
       <c r="D102" s="2">
-        <v>913</v>
+        <v>1500</v>
       </c>
       <c r="E102" s="2">
         <v>2600</v>
@@ -2525,10 +2525,10 @@
         <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>25304</v>
+        <v>27700</v>
       </c>
       <c r="E117" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2545,7 +2545,7 @@
         <v>930</v>
       </c>
       <c r="E118" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>153</v>
       </c>
       <c r="E119" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2579,7 +2579,7 @@
         <v>1712</v>
       </c>
       <c r="E120" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2596,7 +2596,7 @@
         <v>3255</v>
       </c>
       <c r="E121" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -2610,10 +2610,10 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>25304</v>
+        <v>27700</v>
       </c>
       <c r="E122" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -2630,7 +2630,7 @@
         <v>930</v>
       </c>
       <c r="E123" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -2647,7 +2647,7 @@
         <v>153</v>
       </c>
       <c r="E124" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -2664,7 +2664,7 @@
         <v>1712</v>
       </c>
       <c r="E125" s="2">
-        <v>55650</v>
+        <v>55350</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -2681,138 +2681,11 @@
         <v>3255</v>
       </c>
       <c r="E126" s="2">
-        <v>55650</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-    </row>
-    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-    </row>
-    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
-    </row>
-    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-    </row>
-    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
-    </row>
-    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
-    </row>
-    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-    </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-    </row>
-    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
-    </row>
-    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-    </row>
-    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+        <v>55350</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E151" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/08 Agosto/Dasboatdde julio/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/Dasboarth CVS/09 Septiembre/Dasboatdde agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1006" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4A94663-2454-4210-87D4-7DAD6321C297}"/>
+  <xr:revisionPtr revIDLastSave="1010" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0FEAA07-797C-4952-BAC1-30FB079915E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="38">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -146,7 +146,13 @@
     <t xml:space="preserve">SAN CRISTOBAL </t>
   </si>
   <si>
-    <t>Julio</t>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>ACCESORIOS</t>
+  </si>
+  <si>
+    <t>METRO EST. SAN ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -533,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -1083,7 +1089,7 @@
         <v>1500</v>
       </c>
       <c r="E32" s="2">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1100,7 +1106,7 @@
         <v>50</v>
       </c>
       <c r="E33" s="2">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1117,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1134,7 +1140,7 @@
         <v>130</v>
       </c>
       <c r="E35" s="2">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1151,7 +1157,7 @@
         <v>180</v>
       </c>
       <c r="E36" s="2">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1573,7 +1579,7 @@
         <v>30</v>
       </c>
       <c r="D61" s="2">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E61" s="2">
         <v>1100</v>
@@ -1763,7 +1769,7 @@
         <v>1200</v>
       </c>
       <c r="E72" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1780,7 +1786,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1797,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="E74" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -1814,7 +1820,7 @@
         <v>70</v>
       </c>
       <c r="E75" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -1831,7 +1837,7 @@
         <v>90</v>
       </c>
       <c r="E76" s="2">
-        <v>2200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2253,7 +2259,7 @@
         <v>30</v>
       </c>
       <c r="D101" s="2">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E101" s="2">
         <v>6800</v>
@@ -2423,7 +2429,7 @@
         <v>30</v>
       </c>
       <c r="D111" s="2">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="E111" s="2">
         <v>2650</v>
@@ -2528,7 +2534,7 @@
         <v>27700</v>
       </c>
       <c r="E117" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2545,7 +2551,7 @@
         <v>930</v>
       </c>
       <c r="E118" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2562,7 +2568,7 @@
         <v>153</v>
       </c>
       <c r="E119" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2579,7 +2585,7 @@
         <v>1712</v>
       </c>
       <c r="E120" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2593,10 +2599,10 @@
         <v>30</v>
       </c>
       <c r="D121" s="2">
-        <v>3255</v>
+        <v>3360</v>
       </c>
       <c r="E121" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -2613,7 +2619,7 @@
         <v>27700</v>
       </c>
       <c r="E122" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -2630,7 +2636,7 @@
         <v>930</v>
       </c>
       <c r="E123" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -2647,7 +2653,7 @@
         <v>153</v>
       </c>
       <c r="E124" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -2664,7 +2670,7 @@
         <v>1712</v>
       </c>
       <c r="E125" s="2">
-        <v>55350</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -2678,14 +2684,507 @@
         <v>30</v>
       </c>
       <c r="D126" s="2">
-        <v>3255</v>
+        <v>3360</v>
       </c>
       <c r="E126" s="2">
-        <v>55350</v>
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D127" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="E127" s="2">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D128" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="E128" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>35</v>
+      </c>
+      <c r="B129" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D129" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="E129" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D130" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E130" s="2">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D131" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="E131" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D132" s="2">
+        <v>7500000</v>
+      </c>
+      <c r="E132" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D133" s="2">
+        <v>8000000</v>
+      </c>
+      <c r="E133" s="2">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D134" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="E134" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>35</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D135" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="E135" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>35</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D136" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="E136" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>35</v>
+      </c>
+      <c r="B137" t="s">
+        <v>18</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D137" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E137" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>35</v>
+      </c>
+      <c r="B138" t="s">
+        <v>20</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D138" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="E138" s="2">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>35</v>
+      </c>
+      <c r="B139" t="s">
+        <v>21</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D139" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E139" s="2">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>35</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D140" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="E140" s="2">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>35</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D141" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="E141" s="2">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>35</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D142" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="E142" s="2">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>35</v>
+      </c>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D143" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E143" s="2">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>35</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D144" s="2">
+        <v>7000000</v>
+      </c>
+      <c r="E144" s="2">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>35</v>
+      </c>
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D145" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="E145" s="2">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>35</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D146" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="E146" s="2">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>35</v>
+      </c>
+      <c r="B147" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D147" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E147" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>35</v>
+      </c>
+      <c r="B148" t="s">
+        <v>31</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D148" s="2">
+        <v>117000000</v>
+      </c>
+      <c r="E148" s="2">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>35</v>
+      </c>
+      <c r="B149" t="s">
+        <v>33</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D149" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E149" s="2">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>35</v>
+      </c>
+      <c r="B150" t="s">
+        <v>37</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>35</v>
+      </c>
+      <c r="B151" t="s">
+        <v>37</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D151" s="2">
+        <v>8</v>
+      </c>
+      <c r="E151" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" t="s">
+        <v>37</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D152" s="2">
+        <v>2</v>
+      </c>
+      <c r="E152" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>35</v>
+      </c>
+      <c r="B153" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D153" s="2">
+        <v>20</v>
+      </c>
+      <c r="E153" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D154" s="2">
+        <v>25</v>
+      </c>
+      <c r="E154" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D155" s="2">
+        <v>100000</v>
+      </c>
+      <c r="E155" s="2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E126" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="A1:E125" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>